--- a/survey_templates/028_leadership_stories_submission--survey_templates.xlsx
+++ b/survey_templates/028_leadership_stories_submission--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>story_description</t>
+          <t>story_description_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>story_description</t>
+          <t>story_description_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>story_description</t>
+          <t>story_description_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>story_description</t>
+          <t>story_description_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>story_description</t>
+          <t>story_description_6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>When did it happen?</t>
+          <t>Story Description 6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,7 +681,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>story_description</t>
+          <t>story_description_7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>story_description</t>
+          <t>story_description_8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Where did it happen?</t>
+          <t>Story Description 8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>story_description</t>
+          <t>story_description_9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>story_description</t>
+          <t>story_description_10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How long did it take?</t>
+          <t>Story Description 10</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>story_description</t>
+          <t>story_description_11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How long did it take?</t>
+          <t>Story Description 11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -802,9 +802,9 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,102 +827,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>story_description_choices</t>
+          <t>story_description_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'leader',_'value':_'leader'}</t>
+          <t>leader</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Leader', 'value': 'Leader'}</t>
+          <t>Leader</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>story_description_choices</t>
+          <t>story_description_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'manager',_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Manager', 'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>story_description_choices</t>
+          <t>story_description_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'team_member',_'value':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Team Member', 'value': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>story_description_choices</t>
+          <t>story_description_3_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'team',_'value':_'team'}</t>
+          <t>team</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Team', 'value': 'Team'}</t>
+          <t>Team</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>story_description_choices</t>
+          <t>story_description_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'department',_'value':_'department'}</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Department', 'value': 'Department'}</t>
+          <t>Department</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>story_description_choices</t>
+          <t>story_description_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'organization',_'value':_'organization'}</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Organization', 'value': 'Organization'}</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
